--- a/data/cache/travel_cloud_backup.xlsx
+++ b/data/cache/travel_cloud_backup.xlsx
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -35,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +46,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,9 +426,574 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:BY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>record_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>form_type</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>form_date</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>employee_name</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>employee_no</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>department</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>plan_code</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>trip_purpose</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>from_location</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>to_location</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>trip_date_start</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>trip_time_start</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>trip_date_end</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>trip_time_end</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>trip_days</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>transport_tools</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>transportation_type</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>gov_car_no</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>private_car_km</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>private_car_no</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>other_transport_desc</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>expense_rows</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>amount_total</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>amount_total_upper</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>attachments</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>signature_file</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>handler_name</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>project_manager_name</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>department_manager_name</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>accountant_name</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>note_public</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>remarks_internal</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>send_pdf_to_email</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>budget_source</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>owner_name</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>user_email</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>actor_role</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>source_system</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>created_by</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>updated_by</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>submitted_at</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>submitted_by</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>is_deleted</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>deleted_at</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>deleted_by</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>version</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>last_event_id</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>last_synced_at</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>deleted_reason</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>_row_number</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>_sheet_name</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>traveler</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>project_id</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>purpose</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>departure_location_choice</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>destination_location_choice</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>departure_location_other</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>destination_location_other</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>start_date</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>end_date</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>transport_options</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>private_car_plate</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>official_car_plate</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>other_transport</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>attachment_files</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>departure_location</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>destination_location</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>transport_fee_total</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>misc_fee_total</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>lodging_fee_total</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>other_fee_total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>LCL-TRV-20260315170717</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>submitted</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>96006</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="n">
+        <v>4820</v>
+      </c>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>李政憲</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>joli@sahtech.org</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>2026-03-15T17:12:34</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>李政憲</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>115CA008</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>成果發表會</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>台南</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>台北</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>['高鐵', '計程車']</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr"/>
+      <c r="BO2" t="inlineStr"/>
+      <c r="BP2" t="inlineStr"/>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>[{'日期': '2026-03-15', '起訖地點': '台南-台北', '車別': '高鐵', '交通費': 1320, '膳雜費': 200, '住宿費': 1800, '其它': 180, '單據編號': 'A1'}, {'日期': 'None', '起訖地點': '台北-台南', '車別': '高鐵', '交通費': 1320, '膳雜費': 0, '住宿費': 0, '其它': 0, '單據編號': 'A2'}]</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>台南</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>台北</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>台南 → 台北</t>
+        </is>
+      </c>
+      <c r="BV2" t="n">
+        <v>2640</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>200</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>1800</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>180</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -427,9 +1004,1573 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:BY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>record_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>form_type</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>form_date</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>employee_name</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>employee_no</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>department</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>plan_code</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>trip_purpose</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>from_location</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>to_location</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>trip_date_start</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>trip_time_start</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>trip_date_end</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>trip_time_end</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>trip_days</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>transport_tools</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>transportation_type</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>gov_car_no</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>private_car_km</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>private_car_no</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>other_transport_desc</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>expense_rows</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>amount_total</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>amount_total_upper</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>attachments</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>signature_file</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>handler_name</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>project_manager_name</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>department_manager_name</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>accountant_name</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>note_public</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>remarks_internal</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>send_pdf_to_email</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>budget_source</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>owner_name</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>user_email</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>actor_role</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>source_system</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>created_by</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>updated_by</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>submitted_at</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>submitted_by</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>is_deleted</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>deleted_at</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>deleted_by</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>version</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>last_event_id</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>last_synced_at</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>deleted_reason</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>_row_number</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>_sheet_name</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>traveler</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>project_id</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>purpose</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>departure_location_choice</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>destination_location_choice</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>departure_location_other</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>destination_location_other</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>start_date</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>end_date</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>transport_options</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>private_car_plate</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>official_car_plate</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>other_transport</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>details</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>attachment_files</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>departure_location</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>destination_location</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>transport_fee_total</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>misc_fee_total</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>lodging_fee_total</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>other_fee_total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TR104011150304001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>travel</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-03-03T16:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>方澤沛</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>10401</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>化安處</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>115CA011/化學品計畫</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0305，OSHA 定量暴評教學_高雄場</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>台中</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>高雄</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2026-03-04T16:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2026-03-04T16:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>["高鐵","其他"]</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>高鐵,其他</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>台鐵</t>
+        </is>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>[{"日期":"2026-03-05","起訖地點":"","車別":"高鐵","交通費":0,"膳雜費":0,"住宿費":0,"其它":0,"單據編號":""},{"日期":"","起訖地點":"","車別":"台鐵","交通費":0,"膳雜費":0,"住宿費":0,"其它":0,"單據編號":""},{"日期":"","起訖地點":"","車別":"","交通費":0,"膳雜費":0,"住宿費":0,"其它":0,"單據編號":""}]</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>方澤沛</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>方澤沛</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>pbpk@sahtech.org</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>travel</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>2026-03-16T11:26:36.000Z</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>pbpk@sahtech.org</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>2026-03-16T11:26:36.000Z</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>pbpk@sahtech.org</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>草稿列表</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
+      <c r="BO2" t="inlineStr"/>
+      <c r="BP2" t="inlineStr"/>
+      <c r="BQ2" t="inlineStr"/>
+      <c r="BR2" t="inlineStr"/>
+      <c r="BS2" t="inlineStr"/>
+      <c r="BT2" t="inlineStr"/>
+      <c r="BU2" t="inlineStr"/>
+      <c r="BV2" t="inlineStr"/>
+      <c r="BW2" t="inlineStr"/>
+      <c r="BX2" t="inlineStr"/>
+      <c r="BY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>TR104011150224001</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>travel</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-02-23T16:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>方澤沛</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>10401</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>化安處</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>115GO005/指定菸品計畫</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>工作會議，菸品首次申報討論</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>台中</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2026-02-23T16:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2026-02-23T16:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>["計程車","高鐵"]</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>計程車,高鐵</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>[{"日期":"2026-02-25","起訖地點":"","車別":"高鐵","交通費":0,"膳雜費":0,"住宿費":0,"其它":0,"單據編號":""},{"日期":"","起訖地點":"","車別":"計程車","交通費":0,"膳雜費":0,"住宿費":0,"其它":0,"單據編號":""},{"日期":"","起訖地點":"","車別":"","交通費":0,"膳雜費":0,"住宿費":0,"其它":0,"單據編號":""}]</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>方澤沛</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>方澤沛</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>pbpk@sahtech.org</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>travel</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>2026-03-16T11:24:40.000Z</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>pbpk@sahtech.org</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>2026-03-16T11:24:40.000Z</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>pbpk@sahtech.org</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr"/>
+      <c r="BB3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>草稿列表</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr"/>
+      <c r="BF3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr"/>
+      <c r="BH3" t="inlineStr"/>
+      <c r="BI3" t="inlineStr"/>
+      <c r="BJ3" t="inlineStr"/>
+      <c r="BK3" t="inlineStr"/>
+      <c r="BL3" t="inlineStr"/>
+      <c r="BM3" t="inlineStr"/>
+      <c r="BN3" t="inlineStr"/>
+      <c r="BO3" t="inlineStr"/>
+      <c r="BP3" t="inlineStr"/>
+      <c r="BQ3" t="inlineStr"/>
+      <c r="BR3" t="inlineStr"/>
+      <c r="BS3" t="inlineStr"/>
+      <c r="BT3" t="inlineStr"/>
+      <c r="BU3" t="inlineStr"/>
+      <c r="BV3" t="inlineStr"/>
+      <c r="BW3" t="inlineStr"/>
+      <c r="BX3" t="inlineStr"/>
+      <c r="BY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TR960061150316002</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>travel</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-03-15T16:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>李政憲</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>96006</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>化安處</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>115CA006/致癌計畫</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>DomesticTrip_Draft</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2026-03-15T16:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2026-03-15T16:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>[{"日期":"2026-03-16","起訖地點":"","車別":"","交通費":0,"膳雜費":0,"住宿費":0,"其它":0,"單據編號":""}]</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-03-15T16:00:00.000Z</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>李政憲</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>李政憲</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>61c629684e91429cafd4c95ea66da7b8</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>2026-03-16T12:22:20.000Z</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>草稿列表</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr"/>
+      <c r="BH4" t="inlineStr"/>
+      <c r="BI4" t="inlineStr"/>
+      <c r="BJ4" t="inlineStr"/>
+      <c r="BK4" t="inlineStr"/>
+      <c r="BL4" t="inlineStr"/>
+      <c r="BM4" t="inlineStr"/>
+      <c r="BN4" t="inlineStr"/>
+      <c r="BO4" t="inlineStr"/>
+      <c r="BP4" t="inlineStr"/>
+      <c r="BQ4" t="inlineStr"/>
+      <c r="BR4" t="inlineStr"/>
+      <c r="BS4" t="inlineStr"/>
+      <c r="BT4" t="inlineStr"/>
+      <c r="BU4" t="inlineStr"/>
+      <c r="BV4" t="inlineStr"/>
+      <c r="BW4" t="inlineStr"/>
+      <c r="BX4" t="inlineStr"/>
+      <c r="BY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>9600620260315001</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>deleted</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>96006</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="n">
+        <v>3530</v>
+      </c>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>李政憲</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>joli@sahtech.org</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>2026-03-15T20:28:33</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>2026-03-15T20:28:33</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>李政憲</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>115CA008</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>SDG交流會議</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>台南</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>台北</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr"/>
+      <c r="BJ5" t="inlineStr"/>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr"/>
+      <c r="BO5" t="inlineStr"/>
+      <c r="BP5" t="inlineStr"/>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>[{'日期': '2026-03-15', '起訖地點': '台南-台北', '車別': '高鐵', '交通費': 1350, '膳雜費': 200, '住宿費': 1800, '其它': 180, '單據編號': '1'}]</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>台南</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>台北</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>台南 → 台北</t>
+        </is>
+      </c>
+      <c r="BV5" t="n">
+        <v>1350</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>200</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>1800</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>LCL-TRV-20260315180757</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>10401</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>方澤沛</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>pbpk@sahtech.org</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>2026-03-15T18:07:57</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>方澤沛</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>115CA009</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>期中審查</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>台南</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>新北</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>['計程車', '高鐵']</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr"/>
+      <c r="BO6" t="inlineStr"/>
+      <c r="BP6" t="inlineStr"/>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>[{'日期': '2026-03-15', '起訖地點': '板橋車站-職安署', '車別': '計程車', '交通費': 0, '膳雜費': 0, '住宿費': 0, '其它': 0, '單據編號': ''}]</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>台南</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>新北</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>台南 → 新北</t>
+        </is>
+      </c>
+      <c r="BV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>LCL-TRV-20260315180857</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>travel</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>方澤沛</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>10401</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>化安處</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>115CA009</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>期中審查</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>台南 → 新北</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>新北</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>["計程車", "高鐵"]</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>計程車、高鐵</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>[{"日期": "2026-03-15", "起訖地點": "板橋車站-職安署", "車別": "計程車", "交通費": 0, "膳雜費": 0, "住宿費": 0, "其它": 0, "單據編號": ""}]</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>方澤沛</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>pbpk@sahtech.org</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>2026-03-15T18:08:57</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr"/>
+      <c r="BA7" t="inlineStr"/>
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>方澤沛</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>115CA009</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>期中審查</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>台南</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>新北</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr"/>
+      <c r="BJ7" t="inlineStr"/>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>['計程車', '高鐵']</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr"/>
+      <c r="BO7" t="inlineStr"/>
+      <c r="BP7" t="inlineStr"/>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>[{'日期': '2026-03-15', '起訖地點': '板橋車站-職安署', '車別': '計程車', '交通費': 0, '膳雜費': 0, '住宿費': 0, '其它': 0, '單據編號': ''}]</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>台南</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>新北</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr"/>
+      <c r="BV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>